--- a/محلي (Autosaved).xlsx
+++ b/محلي (Autosaved).xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="916"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="916" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="حساب حامد" sheetId="14" r:id="rId1"/>
@@ -20,17 +20,17 @@
     <sheet name="هاني شتا" sheetId="7" r:id="rId11"/>
     <sheet name="نسخة اولية" sheetId="2" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Author</author>
+    <author>الكاتب</author>
   </authors>
   <commentList>
-    <comment ref="M189" authorId="0" shapeId="0">
+    <comment ref="M189" authorId="0">
       <text>
         <r>
           <rPr>
@@ -40,7 +40,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Author:</t>
+          <t>الكاتب:</t>
         </r>
         <r>
           <rPr>
@@ -63,10 +63,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Author</author>
+    <author>الكاتب</author>
   </authors>
   <commentList>
-    <comment ref="M189" authorId="0" shapeId="0">
+    <comment ref="M189" authorId="0">
       <text>
         <r>
           <rPr>
@@ -76,7 +76,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Author:</t>
+          <t>الكاتب:</t>
         </r>
         <r>
           <rPr>
@@ -1286,18 +1286,6 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1338,791 +1326,23 @@
     <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="130">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="#,##0.000"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="#,##0.000"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="#,##0.000"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4036,7 +3256,11 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -4066,6 +3290,25 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -4081,7 +3324,151 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -4149,7 +3536,11 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -4174,7 +3565,59 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="#,##0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4193,7 +3636,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -4218,7 +3665,560 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="#,##0\ [$ج.م.‏-C01]"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="#,##0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="#,##0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -4394,7 +4394,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table510" displayName="Table510" ref="A3:N627" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table510" displayName="Table510" ref="A3:N627" totalsRowCount="1" headerRowDxfId="129" dataDxfId="128">
+  <autoFilter ref="A3:N626">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="محمد توفيق"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="14">
+    <tableColumn id="1" name="م" dataDxfId="127" totalsRowDxfId="126"/>
+    <tableColumn id="2" name="الاسم" dataDxfId="125" totalsRowDxfId="124"/>
+    <tableColumn id="3" name="التاريخ" totalsRowLabel="الاجمالي" dataDxfId="123" totalsRowDxfId="122"/>
+    <tableColumn id="4" name="رقم الايصال" dataDxfId="121" totalsRowDxfId="120"/>
+    <tableColumn id="5" name="العدد" totalsRowFunction="custom" dataDxfId="119" totalsRowDxfId="118">
+      <totalsRowFormula>SUBTOTAL(9,E18:E296)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" name="الفئة" dataDxfId="117" totalsRowDxfId="116"/>
+    <tableColumn id="7" name="السعر" dataDxfId="115" totalsRowDxfId="114"/>
+    <tableColumn id="14" name="خصم" dataDxfId="113" totalsRowDxfId="112"/>
+    <tableColumn id="13" name="مصاريف اخرى" dataDxfId="111" totalsRowDxfId="110"/>
+    <tableColumn id="8" name="الكمية" totalsRowFunction="custom" dataDxfId="109" totalsRowDxfId="108">
+      <calculatedColumnFormula>Table510[[#This Row],[العدد]]*Table510[[#This Row],[الفئة]]</calculatedColumnFormula>
+      <totalsRowFormula>SUBTOTAL(9,J18:J296)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="9" name="اجمالي المبلغ" totalsRowFunction="custom" dataDxfId="107" totalsRowDxfId="106">
+      <calculatedColumnFormula>IF(Table510[[#This Row],[الفئة]]=0.8,Table510[[#This Row],[السعر]]*Table510[[#This Row],[العدد]]+Table510[[#This Row],[مصاريف اخرى]]-Table510[[#This Row],[خصم]],IF(Table510[[#This Row],[الفئة]]=1.6,Table510[[#This Row],[العدد]]*2*Table510[[#This Row],[السعر]]+Table510[[#This Row],[مصاريف اخرى]]-Table510[[#This Row],[خصم]],Table510[[#This Row],[السعر]]*Table510[[#This Row],[الكمية]]+Table510[[#This Row],[مصاريف اخرى]]-Table510[[#This Row],[خصم]]))</calculatedColumnFormula>
+      <totalsRowFormula>SUBTOTAL(9,Table510[اجمالي المبلغ])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="10" name="المبلغ المدفوع" totalsRowFunction="custom" dataDxfId="105" totalsRowDxfId="104">
+      <totalsRowFormula>SUBTOTAL(9,Table510[المبلغ المدفوع])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="11" name="متبقي" totalsRowFunction="custom" dataDxfId="103" totalsRowDxfId="102">
+      <calculatedColumnFormula>Table510[[#This Row],[اجمالي المبلغ]]-Table510[[#This Row],[المبلغ المدفوع]]</calculatedColumnFormula>
+      <totalsRowFormula>SUBTOTAL(9,Table510[متبقي])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="12" name="ملاحظات" dataDxfId="101" totalsRowDxfId="100"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A3:N627" totalsRowCount="1" headerRowDxfId="99" dataDxfId="98">
   <autoFilter ref="A3:N626">
     <filterColumn colId="1">
       <filters>
@@ -4403,194 +4445,152 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="14">
-    <tableColumn id="1" name="م" dataDxfId="41" totalsRowDxfId="27"/>
-    <tableColumn id="2" name="الاسم" dataDxfId="40" totalsRowDxfId="15"/>
-    <tableColumn id="3" name="التاريخ" totalsRowLabel="الاجمالي" dataDxfId="39" totalsRowDxfId="14"/>
-    <tableColumn id="4" name="رقم الايصال" dataDxfId="38" totalsRowDxfId="26"/>
-    <tableColumn id="5" name="العدد" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="25">
+    <tableColumn id="1" name="م" dataDxfId="97" totalsRowDxfId="96"/>
+    <tableColumn id="2" name="الاسم" dataDxfId="95" totalsRowDxfId="94"/>
+    <tableColumn id="3" name="التاريخ" totalsRowLabel="الاجمالي" dataDxfId="93" totalsRowDxfId="92"/>
+    <tableColumn id="4" name="رقم الايصال" dataDxfId="91" totalsRowDxfId="90"/>
+    <tableColumn id="5" name="العدد" totalsRowFunction="custom" dataDxfId="89" totalsRowDxfId="88">
       <totalsRowFormula>SUBTOTAL(9,E18:E296)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="الفئة" dataDxfId="36" totalsRowDxfId="24"/>
-    <tableColumn id="7" name="السعر" dataDxfId="35" totalsRowDxfId="23"/>
-    <tableColumn id="14" name="خصم" dataDxfId="34" totalsRowDxfId="22"/>
-    <tableColumn id="13" name="مصاريف اخرى" dataDxfId="33" totalsRowDxfId="21"/>
-    <tableColumn id="8" name="الكمية" totalsRowFunction="custom" dataDxfId="32" totalsRowDxfId="20">
-      <calculatedColumnFormula>Table510[[#This Row],[العدد]]*Table510[[#This Row],[الفئة]]</calculatedColumnFormula>
-      <totalsRowFormula>SUBTOTAL(9,J18:J296)</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="9" name="اجمالي المبلغ" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="19">
-      <calculatedColumnFormula>IF(Table510[[#This Row],[الفئة]]=0.8,Table510[[#This Row],[السعر]]*Table510[[#This Row],[العدد]]+Table510[[#This Row],[مصاريف اخرى]]-Table510[[#This Row],[خصم]],IF(Table510[[#This Row],[الفئة]]=1.6,Table510[[#This Row],[العدد]]*2*Table510[[#This Row],[السعر]]+Table510[[#This Row],[مصاريف اخرى]]-Table510[[#This Row],[خصم]],Table510[[#This Row],[السعر]]*Table510[[#This Row],[الكمية]]+Table510[[#This Row],[مصاريف اخرى]]-Table510[[#This Row],[خصم]]))</calculatedColumnFormula>
-      <totalsRowFormula>SUBTOTAL(9,Table510[اجمالي المبلغ])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="10" name="المبلغ المدفوع" totalsRowFunction="custom" dataDxfId="30" totalsRowDxfId="18">
-      <totalsRowFormula>SUBTOTAL(9,Table510[المبلغ المدفوع])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="11" name="متبقي" totalsRowFunction="custom" dataDxfId="29" totalsRowDxfId="17">
-      <calculatedColumnFormula>Table510[[#This Row],[اجمالي المبلغ]]-Table510[[#This Row],[المبلغ المدفوع]]</calculatedColumnFormula>
-      <totalsRowFormula>SUBTOTAL(9,Table510[متبقي])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="12" name="ملاحظات" dataDxfId="28" totalsRowDxfId="16"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A3:N627" totalsRowCount="1" headerRowDxfId="129" dataDxfId="128">
-  <autoFilter ref="A3:N626">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="حامد بريد"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="14">
-    <tableColumn id="1" name="م" dataDxfId="127" totalsRowDxfId="13"/>
-    <tableColumn id="2" name="الاسم" dataDxfId="126" totalsRowDxfId="12"/>
-    <tableColumn id="3" name="التاريخ" totalsRowLabel="الاجمالي" dataDxfId="125" totalsRowDxfId="11"/>
-    <tableColumn id="4" name="رقم الايصال" dataDxfId="124" totalsRowDxfId="10"/>
-    <tableColumn id="5" name="العدد" totalsRowFunction="custom" dataDxfId="123" totalsRowDxfId="9">
-      <totalsRowFormula>SUBTOTAL(9,E18:E296)</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="6" name="الفئة" dataDxfId="122" totalsRowDxfId="8"/>
-    <tableColumn id="7" name="السعر" dataDxfId="121" totalsRowDxfId="7"/>
-    <tableColumn id="14" name="خصم" dataDxfId="120" totalsRowDxfId="6"/>
-    <tableColumn id="13" name="مصاريف اخرى" dataDxfId="119" totalsRowDxfId="5"/>
-    <tableColumn id="8" name="الكمية" totalsRowFunction="custom" dataDxfId="44" totalsRowDxfId="4">
+    <tableColumn id="6" name="الفئة" dataDxfId="87" totalsRowDxfId="86"/>
+    <tableColumn id="7" name="السعر" dataDxfId="85" totalsRowDxfId="84"/>
+    <tableColumn id="14" name="خصم" dataDxfId="83" totalsRowDxfId="82"/>
+    <tableColumn id="13" name="مصاريف اخرى" dataDxfId="81" totalsRowDxfId="80"/>
+    <tableColumn id="8" name="الكمية" totalsRowFunction="custom" dataDxfId="79" totalsRowDxfId="78">
       <calculatedColumnFormula>Table5[[#This Row],[العدد]]*Table5[[#This Row],[الفئة]]</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(9,Table5[الكمية])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" name="الاجمالي" totalsRowFunction="custom" dataDxfId="118" totalsRowDxfId="3">
+    <tableColumn id="9" name="الاجمالي" totalsRowFunction="custom" dataDxfId="77" totalsRowDxfId="76">
       <calculatedColumnFormula>IF(Table5[[#This Row],[الفئة]]=0.8,Table5[[#This Row],[السعر]]*Table5[[#This Row],[العدد]]+Table5[[#This Row],[مصاريف اخرى]]-Table5[[#This Row],[خصم]],IF(Table5[[#This Row],[الفئة]]=1.6,Table5[[#This Row],[العدد]]*2*Table5[[#This Row],[السعر]]+Table5[[#This Row],[مصاريف اخرى]]-Table5[[#This Row],[خصم]],Table5[[#This Row],[السعر]]*Table5[[#This Row],[الكمية]]+Table5[[#This Row],[مصاريف اخرى]]-Table5[[#This Row],[خصم]]))</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(9,Table5[الاجمالي])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" name="المبلغ المدفوع" totalsRowFunction="custom" dataDxfId="117" totalsRowDxfId="2">
+    <tableColumn id="10" name="المبلغ المدفوع" totalsRowFunction="custom" dataDxfId="75" totalsRowDxfId="74">
       <totalsRowFormula>SUBTOTAL(9,Table5[المبلغ المدفوع])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" name="متبقي" totalsRowFunction="custom" dataDxfId="116" totalsRowDxfId="1">
+    <tableColumn id="11" name="متبقي" totalsRowFunction="custom" dataDxfId="73" totalsRowDxfId="72">
       <calculatedColumnFormula>Table5[[#This Row],[الاجمالي]]-Table5[[#This Row],[المبلغ المدفوع]]</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(9,Table5[متبقي])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" name="ملاحظات" dataDxfId="115" totalsRowDxfId="0"/>
+    <tableColumn id="12" name="ملاحظات" dataDxfId="71" totalsRowDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A3:G13" totalsRowShown="0" headerRowDxfId="114" headerRowBorderDxfId="113" tableBorderDxfId="112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A3:G13" totalsRowShown="0" headerRowDxfId="69" headerRowBorderDxfId="68" tableBorderDxfId="67">
   <autoFilter ref="A3:G13"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="م" dataDxfId="111"/>
-    <tableColumn id="2" name="التاريخ " dataDxfId="110"/>
-    <tableColumn id="3" name="رقم الايصال" dataDxfId="109"/>
-    <tableColumn id="4" name="توريد بضاعة" dataDxfId="108"/>
-    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="107"/>
-    <tableColumn id="6" name="متبقي" dataDxfId="106"/>
-    <tableColumn id="7" name="ملاحظات" dataDxfId="105"/>
+    <tableColumn id="1" name="م" dataDxfId="66"/>
+    <tableColumn id="2" name="التاريخ " dataDxfId="65"/>
+    <tableColumn id="3" name="رقم الايصال" dataDxfId="64"/>
+    <tableColumn id="4" name="توريد بضاعة" dataDxfId="63"/>
+    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="62"/>
+    <tableColumn id="6" name="متبقي" dataDxfId="61"/>
+    <tableColumn id="7" name="ملاحظات" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table137" displayName="Table137" ref="A3:G18" totalsRowShown="0" headerRowDxfId="104" headerRowBorderDxfId="103" tableBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table137" displayName="Table137" ref="A3:G18" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57">
   <autoFilter ref="A3:G18"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="م" dataDxfId="101"/>
-    <tableColumn id="2" name="التاريخ " dataDxfId="100"/>
-    <tableColumn id="3" name="رقم الايصال" dataDxfId="99"/>
-    <tableColumn id="4" name="توريد بضاعة" dataDxfId="98"/>
-    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="97"/>
-    <tableColumn id="6" name="متبقي" dataDxfId="96"/>
-    <tableColumn id="7" name="ملاحظات" dataDxfId="95"/>
+    <tableColumn id="1" name="م" dataDxfId="56"/>
+    <tableColumn id="2" name="التاريخ " dataDxfId="55"/>
+    <tableColumn id="3" name="رقم الايصال" dataDxfId="54"/>
+    <tableColumn id="4" name="توريد بضاعة" dataDxfId="53"/>
+    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="52"/>
+    <tableColumn id="6" name="متبقي" dataDxfId="51"/>
+    <tableColumn id="7" name="ملاحظات" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table13789" displayName="Table13789" ref="A3:G12" totalsRowShown="0" headerRowDxfId="94" headerRowBorderDxfId="93" tableBorderDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table13789" displayName="Table13789" ref="A3:G12" totalsRowShown="0" headerRowDxfId="49" headerRowBorderDxfId="48" tableBorderDxfId="47">
   <autoFilter ref="A3:G12"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="م" dataDxfId="91"/>
-    <tableColumn id="2" name="التاريخ " dataDxfId="90"/>
-    <tableColumn id="3" name="رقم الايصال" dataDxfId="89"/>
-    <tableColumn id="4" name="توريد بضاعة" dataDxfId="88"/>
-    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="87"/>
-    <tableColumn id="6" name="متبقي" dataDxfId="86"/>
-    <tableColumn id="7" name="ملاحظات" dataDxfId="85"/>
+    <tableColumn id="1" name="م" dataDxfId="46"/>
+    <tableColumn id="2" name="التاريخ " dataDxfId="45"/>
+    <tableColumn id="3" name="رقم الايصال" dataDxfId="44"/>
+    <tableColumn id="4" name="توريد بضاعة" dataDxfId="43"/>
+    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="42"/>
+    <tableColumn id="6" name="متبقي" dataDxfId="41"/>
+    <tableColumn id="7" name="ملاحظات" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table1378" displayName="Table1378" ref="A3:G12" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table1378" displayName="Table1378" ref="A3:G12" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37">
   <autoFilter ref="A3:G12"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="م" dataDxfId="81"/>
-    <tableColumn id="2" name="التاريخ " dataDxfId="80"/>
-    <tableColumn id="3" name="رقم الايصال" dataDxfId="79"/>
-    <tableColumn id="4" name="توريد بضاعة" dataDxfId="78"/>
-    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="77"/>
-    <tableColumn id="6" name="متبقي" dataDxfId="76"/>
-    <tableColumn id="7" name="ملاحظات" dataDxfId="75"/>
+    <tableColumn id="1" name="م" dataDxfId="36"/>
+    <tableColumn id="2" name="التاريخ " dataDxfId="35"/>
+    <tableColumn id="3" name="رقم الايصال" dataDxfId="34"/>
+    <tableColumn id="4" name="توريد بضاعة" dataDxfId="33"/>
+    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="32"/>
+    <tableColumn id="6" name="متبقي" dataDxfId="31"/>
+    <tableColumn id="7" name="ملاحظات" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A3:G22" totalsRowShown="0" headerRowDxfId="74" headerRowBorderDxfId="73" tableBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A3:G22" totalsRowShown="0" headerRowDxfId="29" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A3:G22"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="م" dataDxfId="71"/>
-    <tableColumn id="2" name="التاريخ " dataDxfId="70"/>
-    <tableColumn id="3" name="رقم الايصال" dataDxfId="69"/>
-    <tableColumn id="4" name="توريد بضاعة" dataDxfId="68"/>
-    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="67"/>
-    <tableColumn id="6" name="متبقي" dataDxfId="66"/>
-    <tableColumn id="7" name="ملاحظات" dataDxfId="65"/>
+    <tableColumn id="1" name="م" dataDxfId="26"/>
+    <tableColumn id="2" name="التاريخ " dataDxfId="25"/>
+    <tableColumn id="3" name="رقم الايصال" dataDxfId="24"/>
+    <tableColumn id="4" name="توريد بضاعة" dataDxfId="23"/>
+    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="22"/>
+    <tableColumn id="6" name="متبقي" dataDxfId="21"/>
+    <tableColumn id="7" name="ملاحظات" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:G35" totalsRowShown="0" headerRowDxfId="64" headerRowBorderDxfId="63" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:G35" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17">
   <autoFilter ref="A3:G35"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="م" dataDxfId="61"/>
-    <tableColumn id="2" name="التاريخ " dataDxfId="60"/>
-    <tableColumn id="3" name="رقم الايصال" dataDxfId="59"/>
-    <tableColumn id="4" name="توريد بضاعة" dataDxfId="58"/>
-    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="57"/>
-    <tableColumn id="6" name="متبقي" dataDxfId="56"/>
-    <tableColumn id="7" name="ملاحظات" dataDxfId="55"/>
+    <tableColumn id="1" name="م" dataDxfId="16"/>
+    <tableColumn id="2" name="التاريخ " dataDxfId="15"/>
+    <tableColumn id="3" name="رقم الايصال" dataDxfId="14"/>
+    <tableColumn id="4" name="توريد بضاعة" dataDxfId="13"/>
+    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="12"/>
+    <tableColumn id="6" name="متبقي" dataDxfId="11"/>
+    <tableColumn id="7" name="ملاحظات" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table14" displayName="Table14" ref="A3:G17" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53" tableBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table14" displayName="Table14" ref="A3:G17" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
   <autoFilter ref="A3:G17"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="م" dataDxfId="51"/>
-    <tableColumn id="2" name="التاريخ " dataDxfId="50"/>
-    <tableColumn id="3" name="رقم الايصال" dataDxfId="49"/>
-    <tableColumn id="4" name="توريد بضاعة" dataDxfId="48"/>
-    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="47"/>
-    <tableColumn id="6" name="متبقي" dataDxfId="46"/>
-    <tableColumn id="7" name="ملاحظات" dataDxfId="45"/>
+    <tableColumn id="1" name="م" dataDxfId="6"/>
+    <tableColumn id="2" name="التاريخ " dataDxfId="5"/>
+    <tableColumn id="3" name="رقم الايصال" dataDxfId="4"/>
+    <tableColumn id="4" name="توريد بضاعة" dataDxfId="3"/>
+    <tableColumn id="5" name="المبلغ المستلم" dataDxfId="2"/>
+    <tableColumn id="6" name="متبقي" dataDxfId="1"/>
+    <tableColumn id="7" name="ملاحظات" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="نسق Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4632,7 +4632,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4667,7 +4667,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4884,7 +4884,7 @@
   <cols>
     <col min="1" max="1" width="5.875" style="52" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.625" style="52" customWidth="1"/>
-    <col min="3" max="3" width="0.375" style="52" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="52" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="52" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" style="52" customWidth="1"/>
     <col min="6" max="6" width="9.875" style="52" customWidth="1"/>
@@ -4903,58 +4903,58 @@
     <row r="2" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="K2" s="53">
         <f>SUBTOTAL(9,Table510[اجمالي المبلغ])</f>
-        <v>192660</v>
+        <v>6280</v>
       </c>
       <c r="L2" s="53">
         <f>SUBTOTAL(9,Table510[المبلغ المدفوع])</f>
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="M2" s="53">
         <f>SUBTOTAL(9,Table510[متبقي])</f>
-        <v>62660</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="95" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="99" t="s">
+      <c r="E3" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="99" t="s">
+      <c r="F3" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="G3" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="100" t="s">
+      <c r="H3" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="100" t="s">
+      <c r="I3" s="96" t="s">
         <v>92</v>
       </c>
-      <c r="J3" s="99" t="s">
+      <c r="J3" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="99" t="s">
+      <c r="K3" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="L3" s="99" t="s">
+      <c r="L3" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="99" t="s">
+      <c r="M3" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="101" t="s">
+      <c r="N3" s="97" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="N17" s="60"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="N225" s="60"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="52">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="N226" s="60"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="52">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="N227" s="60"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="52">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="N228" s="60"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="52">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="N229" s="60"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="52">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="N230" s="60"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="52">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="N231" s="60"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="52">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="N232" s="60"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="52">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="N291" s="60"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="52">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="N292" s="60"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="52">
         <f>A292+1</f>
         <v>290</v>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="N293" s="60"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="52">
         <f>A293+1</f>
         <v>291</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="N294" s="60"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="52">
         <f>A294+1</f>
         <v>292</v>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="N295" s="60"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="52">
         <f>A295+1</f>
         <v>293</v>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="N434" s="60"/>
     </row>
-    <row r="435" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A435" s="52">
         <f t="shared" si="6"/>
         <v>432</v>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="N435" s="60"/>
     </row>
-    <row r="436" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A436" s="52">
         <f t="shared" si="6"/>
         <v>433</v>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="N436" s="60"/>
     </row>
-    <row r="437" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A437" s="52">
         <f t="shared" si="6"/>
         <v>434</v>
@@ -26742,14 +26742,14 @@
       <c r="N626" s="60"/>
     </row>
     <row r="627" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B627" s="102"/>
-      <c r="C627" s="103" t="s">
+      <c r="B627" s="98"/>
+      <c r="C627" s="99" t="s">
         <v>18</v>
       </c>
       <c r="D627" s="55"/>
       <c r="E627" s="93">
         <f>SUBTOTAL(9,E18:E296)</f>
-        <v>1066</v>
+        <v>0</v>
       </c>
       <c r="F627" s="59"/>
       <c r="G627" s="57"/>
@@ -26757,25 +26757,25 @@
       <c r="I627" s="57"/>
       <c r="J627" s="93">
         <f>SUBTOTAL(9,J18:J296)</f>
-        <v>5052</v>
+        <v>0</v>
       </c>
       <c r="K627" s="91">
         <f>SUBTOTAL(9,Table510[اجمالي المبلغ])</f>
-        <v>192660</v>
+        <v>6280</v>
       </c>
       <c r="L627" s="92">
         <f>SUBTOTAL(9,Table510[المبلغ المدفوع])</f>
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="M627" s="92">
         <f>SUBTOTAL(9,Table510[متبقي])</f>
-        <v>62660</v>
+        <v>6280</v>
       </c>
       <c r="N627" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="73" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="68" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
@@ -27443,11 +27443,11 @@
       <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:8" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="94" t="s">
+      <c r="A36" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
+      <c r="B36" s="109"/>
+      <c r="C36" s="109"/>
       <c r="D36" s="18">
         <f>SUM(D4:D35)</f>
         <v>333687</v>
@@ -27858,11 +27858,11 @@
       </c>
       <c r="G3" s="24"/>
       <c r="H3" s="25"/>
-      <c r="N3" s="96">
+      <c r="N3" s="110">
         <f>N4+O4</f>
         <v>2227432</v>
       </c>
-      <c r="O3" s="97"/>
+      <c r="O3" s="111"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="26">
@@ -52200,37 +52200,37 @@
       <c r="N626" s="60"/>
     </row>
     <row r="627" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A627" s="104"/>
-      <c r="B627" s="105"/>
-      <c r="C627" s="106" t="s">
+      <c r="A627" s="100"/>
+      <c r="B627" s="101"/>
+      <c r="C627" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="D627" s="105"/>
-      <c r="E627" s="107">
+      <c r="D627" s="101"/>
+      <c r="E627" s="103">
         <f>SUBTOTAL(9,E18:E296)</f>
         <v>870</v>
       </c>
-      <c r="F627" s="108"/>
-      <c r="G627" s="109"/>
-      <c r="H627" s="109"/>
-      <c r="I627" s="109"/>
-      <c r="J627" s="107">
+      <c r="F627" s="104"/>
+      <c r="G627" s="105"/>
+      <c r="H627" s="105"/>
+      <c r="I627" s="105"/>
+      <c r="J627" s="103">
         <f>SUBTOTAL(9,Table5[الكمية])</f>
         <v>4064</v>
       </c>
-      <c r="K627" s="110">
+      <c r="K627" s="106">
         <f>SUBTOTAL(9,Table5[الاجمالي])</f>
         <v>155015</v>
       </c>
-      <c r="L627" s="111">
+      <c r="L627" s="107">
         <f>SUBTOTAL(9,Table5[المبلغ المدفوع])</f>
         <v>185925</v>
       </c>
-      <c r="M627" s="111">
+      <c r="M627" s="107">
         <f>SUBTOTAL(9,Table5[متبقي])</f>
         <v>-30910</v>
       </c>
-      <c r="N627" s="109"/>
+      <c r="N627" s="105"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
